--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -662,6 +662,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>parallel(charfadeout(L,1);charfadeout(R,1))&amp;loadScript(</t>
     </r>
     <r>
@@ -764,6 +769,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1070,6 +1080,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1109,12 +1124,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>loadScript(</t>
+      <t>charfadein(L,1)&amp;loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -6590,9 +6600,7 @@
       <c r="J99" t="s">
         <v>15</v>
       </c>
-      <c r="K99" t="s">
-        <v>15</v>
-      </c>
+      <c r="K99"/>
       <c r="L99" t="s">
         <v>300</v>
       </c>
@@ -6608,7 +6616,7 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E100" t="s">
         <v>15</v>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（终）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="484">
   <si>
     <t>ID</t>
   </si>
@@ -541,6 +541,9 @@
     <t>他们是不是告诉你，我因为不成熟的手术条件，被造梦设备逼疯了。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=20</t>
   </si>
   <si>
@@ -750,6 +753,9 @@
     <t>他们给我设定了公司职员的身份，给我灌输了可以靠价值大小决定人命归属的理念，给我下达了训练那些病人的任务，直到我发现这一切都是被人精心伪造的。发现自己也只是和那些病人一样，可以随意丢弃的工具。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
@@ -977,6 +983,9 @@
     <t>只听一声电流的轻响在耳边闪过，一旁闲置的几块电脑屏幕骤然亮起冷白色的光芒，屏幕上整齐罗列着一份份加密的实验档案，最上方的标题处赫然写着一行加粗的英文——“圣徒计划”。</t>
   </si>
   <si>
+    <t>6 enhanced oceanframemusic-horror-background-music</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_clark4F(4)_49,1)</t>
   </si>
   <si>
@@ -1124,6 +1133,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadein(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -4356,7 +4370,7 @@
         <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="J40" t="s">
         <v>15</v>
@@ -4365,12 +4379,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" ht="30" spans="1:12">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
         <v>32</v>
@@ -4388,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4403,12 +4417,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4426,7 +4440,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4441,12 +4455,12 @@
         <v>45</v>
       </c>
       <c r="L42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" ht="42" spans="1:12">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
         <v>32</v>
@@ -4464,7 +4478,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4479,12 +4493,12 @@
         <v>35</v>
       </c>
       <c r="L43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4502,7 +4516,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4517,12 +4531,12 @@
         <v>45</v>
       </c>
       <c r="L44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4540,7 +4554,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4555,12 +4569,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
         <v>32</v>
@@ -4578,7 +4592,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4593,12 +4607,12 @@
         <v>35</v>
       </c>
       <c r="L46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4616,7 +4630,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4631,12 +4645,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" ht="70.5" spans="1:12">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B48" t="s">
         <v>32</v>
@@ -4654,7 +4668,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4669,12 +4683,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s">
         <v>108</v>
@@ -4692,7 +4706,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4707,12 +4721,12 @@
         <v>45</v>
       </c>
       <c r="L49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4730,7 +4744,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4742,12 +4756,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B51" t="s">
         <v>108</v>
@@ -4765,7 +4779,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4780,12 +4794,12 @@
         <v>35</v>
       </c>
       <c r="L51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B52" t="s">
         <v>32</v>
@@ -4803,7 +4817,7 @@
         <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4815,15 +4829,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4841,7 +4855,7 @@
         <v>33</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4853,15 +4867,15 @@
         <v>15</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" ht="150" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
         <v>32</v>
@@ -4879,7 +4893,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4894,12 +4908,12 @@
         <v>35</v>
       </c>
       <c r="L54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
         <v>28</v>
@@ -4917,7 +4931,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4932,12 +4946,12 @@
         <v>45</v>
       </c>
       <c r="L55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
         <v>32</v>
@@ -4955,7 +4969,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4970,12 +4984,12 @@
         <v>35</v>
       </c>
       <c r="L56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4993,7 +5007,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5013,7 +5027,7 @@
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>32</v>
@@ -5031,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5051,7 +5065,7 @@
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
         <v>28</v>
@@ -5069,7 +5083,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5084,12 +5098,12 @@
         <v>45</v>
       </c>
       <c r="L59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" ht="30" spans="1:12">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s">
         <v>32</v>
@@ -5107,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5127,7 +5141,7 @@
     </row>
     <row r="61" ht="67.5" spans="1:12">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B61" t="s">
         <v>32</v>
@@ -5145,13 +5159,13 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="J61" t="s">
         <v>15</v>
@@ -5160,12 +5174,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" ht="55.5" spans="1:12">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
@@ -5183,7 +5197,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5198,12 +5212,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5221,7 +5235,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5236,12 +5250,12 @@
         <v>45</v>
       </c>
       <c r="L63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5259,7 +5273,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5271,15 +5285,15 @@
         <v>15</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" ht="150" spans="1:12">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5297,7 +5311,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5312,12 +5326,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B66" t="s">
         <v>108</v>
@@ -5335,7 +5349,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5350,12 +5364,12 @@
         <v>35</v>
       </c>
       <c r="L66" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5373,7 +5387,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5393,7 +5407,7 @@
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B68" t="s">
         <v>108</v>
@@ -5411,7 +5425,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5426,12 +5440,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B69" t="s">
         <v>108</v>
@@ -5449,7 +5463,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5464,12 +5478,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5487,7 +5501,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5507,7 +5521,7 @@
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
         <v>32</v>
@@ -5525,7 +5539,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5545,7 +5559,7 @@
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5563,7 +5577,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5578,12 +5592,12 @@
         <v>45</v>
       </c>
       <c r="L72" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B73" t="s">
         <v>32</v>
@@ -5601,7 +5615,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5621,7 +5635,7 @@
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B74" t="s">
         <v>32</v>
@@ -5639,7 +5653,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5654,12 +5668,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="75" ht="69" spans="1:12">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5677,7 +5691,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5692,21 +5706,21 @@
         <v>45</v>
       </c>
       <c r="L75" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" ht="27" spans="1:12">
       <c r="A76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5715,7 +5729,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5730,12 +5744,12 @@
         <v>35</v>
       </c>
       <c r="L76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5744,7 +5758,7 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5753,7 +5767,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5768,12 +5782,12 @@
         <v>45</v>
       </c>
       <c r="L77" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" ht="27" spans="1:12">
       <c r="A78" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5791,7 +5805,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5811,7 +5825,7 @@
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B79" t="s">
         <v>32</v>
@@ -5829,7 +5843,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5844,12 +5858,12 @@
         <v>35</v>
       </c>
       <c r="L79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" ht="54" spans="1:12">
       <c r="A80" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
@@ -5867,7 +5881,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5882,12 +5896,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B81" t="s">
         <v>28</v>
@@ -5905,7 +5919,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5920,12 +5934,12 @@
         <v>45</v>
       </c>
       <c r="L81" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82" ht="55.5" spans="1:12">
       <c r="A82" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5943,7 +5957,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5963,7 +5977,7 @@
     </row>
     <row r="83" ht="54" spans="1:12">
       <c r="A83" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5981,7 +5995,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5996,12 +6010,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" ht="27" spans="1:12">
       <c r="A84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6019,7 +6033,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6034,12 +6048,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6057,7 +6071,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6072,12 +6086,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="86" ht="55.5" spans="1:12">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" ht="60" spans="1:12">
       <c r="A86" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6095,27 +6109,27 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
       </c>
       <c r="I86" t="s">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="J86" t="s">
         <v>15</v>
       </c>
       <c r="K86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B87" t="s">
         <v>28</v>
@@ -6133,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6148,12 +6162,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B88" t="s">
         <v>32</v>
@@ -6171,7 +6185,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6186,12 +6200,12 @@
         <v>35</v>
       </c>
       <c r="L88" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" ht="54" spans="1:12">
       <c r="A89" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6209,7 +6223,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6224,12 +6238,12 @@
         <v>45</v>
       </c>
       <c r="L89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6247,7 +6261,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6262,12 +6276,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" ht="55.5" spans="1:12">
       <c r="A91" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6285,7 +6299,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6300,21 +6314,21 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B92" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6323,7 +6337,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6338,12 +6352,12 @@
         <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="93" ht="27" spans="1:12">
       <c r="A93" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6352,7 +6366,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6361,7 +6375,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6376,21 +6390,21 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B94" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -6399,7 +6413,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6414,12 +6428,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" ht="58.5" spans="1:12">
       <c r="A95" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6428,7 +6442,7 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -6437,7 +6451,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6452,12 +6466,12 @@
         <v>45</v>
       </c>
       <c r="L95" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" ht="27" spans="1:12">
       <c r="A96" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6475,7 +6489,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6490,12 +6504,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6513,7 +6527,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6528,12 +6542,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6551,7 +6565,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6563,15 +6577,15 @@
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L98" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" ht="150" spans="1:12">
       <c r="A99" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6589,7 +6603,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6600,14 +6614,13 @@
       <c r="J99" t="s">
         <v>15</v>
       </c>
-      <c r="K99"/>
       <c r="L99" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100" ht="40.5" spans="1:12">
       <c r="A100" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B100" t="s">
         <v>32</v>
@@ -6625,7 +6638,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6637,10 +6650,10 @@
         <v>15</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L100" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -6661,39 +6674,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6701,15 +6714,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6717,7 +6730,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -6725,58 +6738,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6798,616 +6811,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F7" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F9" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E12" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E13" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F13" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F14" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E15" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E16" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F16" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F17" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C18" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D18" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F18" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F19" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F20" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D21" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E21" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F21" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B22" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D22" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E22" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F22" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D23" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E23" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B24" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C24" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D24" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F24" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B25" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C25" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D25" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E25" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F25" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C26" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D26" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F26" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F27" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
+        <v>466</v>
+      </c>
+      <c r="C28" t="s">
+        <v>467</v>
+      </c>
+      <c r="D28" t="s">
         <v>463</v>
       </c>
-      <c r="C28" t="s">
-        <v>464</v>
-      </c>
-      <c r="D28" t="s">
-        <v>460</v>
-      </c>
       <c r="E28" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F28" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F29" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B30" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F30" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B31" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C31" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D31" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（终）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="485">
   <si>
     <t>ID</t>
   </si>
@@ -478,7 +478,70 @@
     </r>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=13; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_Sophia; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=13; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端详飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立刻离开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>73</t>
@@ -686,7 +749,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>, 8))</t>
+      <t>, 8)</t>
     </r>
   </si>
   <si>
@@ -699,7 +762,70 @@
     <t>为了证实我被创造的意义，为了扯下人类那伪善的面具，为了求证生命与生命之间，是否可以用价值进行比较，就像那些人要求我做的那些事情一样。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Abaddon; 层级=13; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_Abaddon; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=13; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立刻离开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>94</t>
@@ -754,6 +880,9 @@
   </si>
   <si>
     <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music7)</t>
   </si>
   <si>
     <t>101</t>
@@ -986,7 +1115,7 @@
     <t>6 enhanced oceanframemusic-horror-background-music</t>
   </si>
   <si>
-    <t>bgfade(sntzm_clark4F(4)_49,1)</t>
+    <t>bgfade(sntzm_clark4F(4)_49,1)&amp;unlockmusic(Music6)</t>
   </si>
   <si>
     <t>50</t>
@@ -4112,7 +4241,7 @@
       <c r="K33" t="s">
         <v>35</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" s="2" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4907,7 +5036,7 @@
       <c r="K54" t="s">
         <v>35</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" s="2" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5171,7 +5300,7 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="L61" t="s">
         <v>133</v>
@@ -5179,7 +5308,7 @@
     </row>
     <row r="62" ht="55.5" spans="1:12">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
@@ -5197,7 +5326,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5217,7 +5346,7 @@
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5235,7 +5364,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5255,7 +5384,7 @@
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5273,7 +5402,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5285,15 +5414,15 @@
         <v>15</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" ht="150" spans="1:12">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5311,7 +5440,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5326,12 +5455,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B66" t="s">
         <v>108</v>
@@ -5349,7 +5478,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5364,12 +5493,12 @@
         <v>35</v>
       </c>
       <c r="L66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5387,7 +5516,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5407,7 +5536,7 @@
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B68" t="s">
         <v>108</v>
@@ -5425,7 +5554,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5440,12 +5569,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
         <v>108</v>
@@ -5463,7 +5592,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5478,12 +5607,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5501,7 +5630,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5521,7 +5650,7 @@
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
         <v>32</v>
@@ -5539,7 +5668,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5559,7 +5688,7 @@
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5577,7 +5706,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5592,12 +5721,12 @@
         <v>45</v>
       </c>
       <c r="L72" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B73" t="s">
         <v>32</v>
@@ -5615,7 +5744,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5635,7 +5764,7 @@
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B74" t="s">
         <v>32</v>
@@ -5653,7 +5782,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5668,12 +5797,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" ht="69" spans="1:12">
       <c r="A75" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5691,7 +5820,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5706,21 +5835,21 @@
         <v>45</v>
       </c>
       <c r="L75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" ht="27" spans="1:12">
       <c r="A76" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5729,7 +5858,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5744,12 +5873,12 @@
         <v>35</v>
       </c>
       <c r="L76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5758,7 +5887,7 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5767,7 +5896,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5782,12 +5911,12 @@
         <v>45</v>
       </c>
       <c r="L77" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="78" ht="27" spans="1:12">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5805,7 +5934,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5825,7 +5954,7 @@
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
         <v>32</v>
@@ -5843,7 +5972,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5863,7 +5992,7 @@
     </row>
     <row r="80" ht="54" spans="1:12">
       <c r="A80" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
@@ -5881,7 +6010,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5896,12 +6025,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B81" t="s">
         <v>28</v>
@@ -5919,7 +6048,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5934,12 +6063,12 @@
         <v>45</v>
       </c>
       <c r="L81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" ht="55.5" spans="1:12">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5957,7 +6086,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5977,7 +6106,7 @@
     </row>
     <row r="83" ht="54" spans="1:12">
       <c r="A83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5995,7 +6124,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6010,12 +6139,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" ht="27" spans="1:12">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6033,7 +6162,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6048,12 +6177,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6071,7 +6200,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6086,12 +6215,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" ht="60" spans="1:12">
       <c r="A86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6109,19 +6238,19 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
       </c>
       <c r="I86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J86" t="s">
         <v>15</v>
       </c>
       <c r="K86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L86" t="s">
         <v>139</v>
@@ -6129,7 +6258,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B87" t="s">
         <v>28</v>
@@ -6147,7 +6276,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6162,12 +6291,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B88" t="s">
         <v>32</v>
@@ -6185,7 +6314,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6200,12 +6329,12 @@
         <v>35</v>
       </c>
       <c r="L88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" ht="54" spans="1:12">
       <c r="A89" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6223,7 +6352,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6243,7 +6372,7 @@
     </row>
     <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6261,7 +6390,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6276,12 +6405,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" ht="55.5" spans="1:12">
       <c r="A91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6299,7 +6428,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6319,16 +6448,16 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6337,7 +6466,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6352,12 +6481,12 @@
         <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="93" ht="27" spans="1:12">
       <c r="A93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6366,7 +6495,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6375,7 +6504,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6390,21 +6519,21 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B94" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -6413,7 +6542,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6428,12 +6557,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" ht="58.5" spans="1:12">
       <c r="A95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6442,7 +6571,7 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -6451,7 +6580,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6466,12 +6595,12 @@
         <v>45</v>
       </c>
       <c r="L95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" ht="27" spans="1:12">
       <c r="A96" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6489,7 +6618,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6504,12 +6633,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6527,7 +6656,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6542,12 +6671,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6565,7 +6694,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6577,15 +6706,15 @@
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99" ht="150" spans="1:12">
       <c r="A99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6603,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6615,12 +6744,12 @@
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100" ht="40.5" spans="1:12">
       <c r="A100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B100" t="s">
         <v>32</v>
@@ -6638,7 +6767,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6650,10 +6779,10 @@
         <v>15</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L100" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -6674,31 +6803,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B4" t="s">
         <v>191</v>
@@ -6706,7 +6835,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6714,15 +6843,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6730,7 +6859,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -6738,58 +6867,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -6811,616 +6940,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F15" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F17" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D20" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F20" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F21" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C22" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E22" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F22" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D23" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E24" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F25" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C26" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F27" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B28" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C28" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C30" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F30" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B31" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C31" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D31" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
